--- a/converted_files/837/837I-minimal.xlsx
+++ b/converted_files/837/837I-minimal.xlsx
@@ -1872,7 +1872,7 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>69e82c69836d7d05c9a05619</t>
+          <t>6a04cb3c618f76c4f7b194ca</t>
         </is>
       </c>
       <c r="B2" s="3" t="inlineStr">
@@ -2577,7 +2577,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>69e82c69836d7d05c9a05619</t>
+          <t>6a04cb3c618f76c4f7b194ca</t>
         </is>
       </c>
       <c r="B3"/>

--- a/converted_files/837/837I-minimal.xlsx
+++ b/converted_files/837/837I-minimal.xlsx
@@ -1872,7 +1872,7 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>6a04cb3c618f76c4f7b194ca</t>
+          <t>6a04cc5c1ef26d534baf3fd8</t>
         </is>
       </c>
       <c r="B2" s="3" t="inlineStr">
@@ -2577,7 +2577,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>6a04cb3c618f76c4f7b194ca</t>
+          <t>6a04cc5c1ef26d534baf3fd8</t>
         </is>
       </c>
       <c r="B3"/>

--- a/converted_files/837/837I-minimal.xlsx
+++ b/converted_files/837/837I-minimal.xlsx
@@ -1872,7 +1872,7 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>6a04cc5c1ef26d534baf3fd8</t>
+          <t>6a0614def8d6a2fc74348e22</t>
         </is>
       </c>
       <c r="B2" s="3" t="inlineStr">
@@ -2577,7 +2577,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>6a04cc5c1ef26d534baf3fd8</t>
+          <t>6a0614def8d6a2fc74348e22</t>
         </is>
       </c>
       <c r="B3"/>

--- a/converted_files/837/837I-minimal.xlsx
+++ b/converted_files/837/837I-minimal.xlsx
@@ -1872,7 +1872,7 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>6a0614def8d6a2fc74348e22</t>
+          <t>6a32cb6497613a0e499094f4</t>
         </is>
       </c>
       <c r="B2" s="3" t="inlineStr">
@@ -2577,7 +2577,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>6a0614def8d6a2fc74348e22</t>
+          <t>6a32cb6497613a0e499094f4</t>
         </is>
       </c>
       <c r="B3"/>
